--- a/data/trans_camb/IP1007-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,9</t>
+          <t>-0,41; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,31</t>
+          <t>-0,41; 2,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,24</t>
+          <t>-1,67; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,79</t>
+          <t>-0,6; 0,88</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-2,96; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,0</t>
+          <t>-3,2; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,0</t>
+          <t>-1,39; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,0</t>
+          <t>-1,37; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,17</t>
+          <t>-0,63; 1,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,11</t>
+          <t>-0,63; 1,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,39</t>
+          <t>-0,93; 0,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,37</t>
+          <t>-0,96; 0,24</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,45</t>
+          <t>-0,44; 0,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,49</t>
+          <t>-0,44; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,01</t>
+          <t>-0,87; -0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,26</t>
+          <t>-0,71; 0,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,07</t>
+          <t>-0,52; 0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,15</t>
+          <t>-0,46; 0,18</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 238,65</t>
+          <t>-100,0; 247,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,49</t>
+          <t>-100,0; 95,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 130,64</t>
+          <t>-88,13; 148,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,53</t>
+          <t>-0,41; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,55</t>
+          <t>-0,41; 2,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,8; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,41</t>
+          <t>-1,42; 0,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,36</t>
+          <t>-0,8; 0,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,88</t>
+          <t>-0,56; 0,77</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,0</t>
+          <t>-2,69; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,72; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,52</t>
+          <t>-0,63; 1,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,14</t>
+          <t>-0,63; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,32</t>
+          <t>-0,93; 0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,24</t>
+          <t>-0,93; 0,37</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,4</t>
+          <t>-0,42; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,42</t>
+          <t>-0,43; 0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; -0,0</t>
+          <t>-0,92; 0,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,26</t>
+          <t>-0,74; 0,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,09</t>
+          <t>-0,53; 0,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,18</t>
+          <t>-0,45; 0,17</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 247,82</t>
+          <t>-100,0; 199,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,99</t>
+          <t>-100,0; 66,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 148,31</t>
+          <t>-87,82; 124,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,52</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,66</t>
+          <t>-1,65; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,0</t>
+          <t>-0,41; 1,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,45</t>
+          <t>-0,41; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,33</t>
+          <t>-0,73; 0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,77</t>
+          <t>-0,58; 0,79</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-56,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>84,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>167,27%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-56,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,03; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-1,48; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,0</t>
+          <t>-1,58; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-0,62; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-0,63; 1,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,25</t>
+          <t>-2,34; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,41</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,37</t>
+          <t>-0,91; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,37</t>
+          <t>-0,88; 0,37</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-0,91; 0,01</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-0,75; 0,26</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>-0,42; 0,45</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 0,41</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 0,01</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,25</t>
+          <t>-0,44; 0,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,05</t>
+          <t>-0,54; 0,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,17</t>
+          <t>-0,48; 0,15</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-79,68%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-42,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-18,88%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-35,28%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-79,68%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-42,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 238,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,63</t>
+          <t>-100,0; 75,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,82; 124,97</t>
+          <t>-86,78; 130,64</t>
         </is>
       </c>
     </row>
